--- a/Data/Home/Bathroom.WaterHeater001.xlsx
+++ b/Data/Home/Bathroom.WaterHeater001.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H141"/>
+  <dimension ref="A1:I119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709249911</v>
+        <v>1711872872</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -497,14 +502,15 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
+          <t>Bathroom.WaterHeater001.state: on</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -523,7 +529,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709251942</v>
+        <v>1711877938</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -541,6 +547,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -559,7 +566,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709279067</v>
+        <v>1711891533</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -577,6 +584,7 @@
           <t>cyber</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -595,7 +603,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709284473</v>
+        <v>1711973548</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -613,6 +621,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -631,7 +640,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709245753</v>
+        <v>1711975804</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -649,6 +658,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -667,7 +677,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709329896</v>
+        <v>1711977219</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -685,6 +695,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -703,7 +714,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709349412</v>
+        <v>1712049275</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -721,6 +732,7 @@
           <t>cyber</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -739,7 +751,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709448034</v>
+        <v>1712052278</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -757,6 +769,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -775,7 +788,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709452931</v>
+        <v>1712060377</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -785,14 +798,15 @@
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: on</t>
+          <t>Bathroom.WaterHeater001.state: off</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -811,7 +825,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709454697</v>
+        <v>1712137954</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -821,14 +835,15 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
+          <t>Bathroom.WaterHeater001.state: on</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -847,7 +862,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709455356</v>
+        <v>1712141391</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -865,6 +880,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -883,7 +899,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709532209</v>
+        <v>1712142206</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -893,14 +909,15 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: on</t>
+          <t>Bathroom.WaterHeater001.state: off</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -919,7 +936,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709542910</v>
+        <v>1712144389</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -929,14 +946,15 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
+          <t>Bathroom.WaterHeater001.state: on</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -955,7 +973,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709588623</v>
+        <v>1712147275</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -973,6 +991,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -991,7 +1010,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709612043</v>
+        <v>1712149567</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1001,14 +1020,15 @@
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: on</t>
+          <t>Bathroom.WaterHeater001.state: off</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1027,7 +1047,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709620075</v>
+        <v>1712187407</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1037,7 +1057,7 @@
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
+          <t>Bathroom.WaterHeater001.state: on</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1045,6 +1065,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1063,7 +1084,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709620388</v>
+        <v>1712225338</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1073,14 +1094,15 @@
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: on</t>
+          <t>Bathroom.WaterHeater001.state: off</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1099,7 +1121,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709622471</v>
+        <v>1712273859</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1109,7 +1131,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
+          <t>Bathroom.WaterHeater001.state: on</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1117,6 +1139,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1135,7 +1158,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709628535</v>
+        <v>1712365737</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1145,7 +1168,7 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: on</t>
+          <t>Bathroom.WaterHeater001.state: off</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1153,6 +1176,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1171,7 +1195,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709628810</v>
+        <v>1712367753</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1181,7 +1205,7 @@
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
+          <t>Bathroom.WaterHeater001.state: on</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1189,6 +1213,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1207,7 +1232,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709633896</v>
+        <v>1712383116</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1225,6 +1250,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1243,7 +1269,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709680018</v>
+        <v>1712392822</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1261,6 +1287,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1279,7 +1306,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709680964</v>
+        <v>1712394621</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1297,6 +1324,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1315,7 +1343,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709694195</v>
+        <v>1712400408</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1325,7 +1353,7 @@
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
+          <t>Bathroom.WaterHeater001.state: on</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1333,6 +1361,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1351,7 +1380,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709702030</v>
+        <v>1712451665</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1361,7 +1390,7 @@
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: on</t>
+          <t>Bathroom.WaterHeater001.state: off</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1369,6 +1398,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1387,7 +1417,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709711729</v>
+        <v>1712453195</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1397,14 +1427,15 @@
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
+          <t>Bathroom.WaterHeater001.state: on</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1423,7 +1454,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709766843</v>
+        <v>1712456481</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1441,6 +1472,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1459,7 +1491,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709768417</v>
+        <v>1712465706</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1474,9 +1506,10 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1495,7 +1528,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709770229</v>
+        <v>1712467369</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1513,6 +1546,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1531,7 +1565,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709788772</v>
+        <v>1712487884</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1549,6 +1583,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1567,7 +1602,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709793011</v>
+        <v>1712491818</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1585,6 +1620,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1603,7 +1639,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709796628</v>
+        <v>1712498897</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1621,6 +1657,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1639,7 +1676,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709799514</v>
+        <v>1712506183</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1657,6 +1694,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1675,7 +1713,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709804703</v>
+        <v>1712532795</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1685,7 +1723,7 @@
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: on</t>
+          <t>Bathroom.WaterHeater001.state: off</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -1693,6 +1731,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1711,7 +1750,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709873860</v>
+        <v>1712561957</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1729,6 +1768,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1747,7 +1787,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709883529</v>
+        <v>1712568928</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1762,9 +1802,10 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1783,7 +1824,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709967647</v>
+        <v>1712656678</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1801,6 +1842,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1819,7 +1861,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709971227</v>
+        <v>1712657575</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1837,6 +1879,7 @@
           <t>cyber</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1855,7 +1898,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709973474</v>
+        <v>1712660535</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1873,6 +1916,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1891,7 +1935,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709974635</v>
+        <v>1712707774</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1909,6 +1953,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1927,7 +1972,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1710021863</v>
+        <v>1712746221</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1945,6 +1990,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1963,7 +2009,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1710033864</v>
+        <v>1712752931</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1978,9 +2024,10 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1999,7 +2046,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1710034818</v>
+        <v>1712755752</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2017,6 +2064,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2035,7 +2083,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1710049653</v>
+        <v>1712791090</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2050,9 +2098,10 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2071,7 +2120,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1710052002</v>
+        <v>1712830516</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2089,6 +2138,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2107,7 +2157,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1710053989</v>
+        <v>1712830955</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2125,6 +2175,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2143,7 +2194,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1710195615</v>
+        <v>1712974570</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2161,6 +2212,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2179,7 +2231,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1710198174</v>
+        <v>1712975654</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2197,6 +2249,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2215,7 +2268,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1710220307</v>
+        <v>1712997089</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2225,14 +2278,15 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: on</t>
+          <t>Bathroom.WaterHeater001.state: off</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2251,7 +2305,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1710227742</v>
+        <v>1713005842</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2261,7 +2315,7 @@
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
+          <t>Bathroom.WaterHeater001.state: on</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2269,6 +2323,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2287,7 +2342,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1710233283</v>
+        <v>1713012850</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2297,14 +2352,15 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: on</t>
+          <t>Bathroom.WaterHeater001.state: off</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2323,7 +2379,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1710236250</v>
+        <v>1713014655</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2333,7 +2389,7 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
+          <t>Bathroom.WaterHeater001.state: on</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2341,6 +2397,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2359,7 +2416,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1710288459</v>
+        <v>1713058349</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2369,14 +2426,15 @@
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: on</t>
+          <t>Bathroom.WaterHeater001.state: off</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2395,7 +2453,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1710292332</v>
+        <v>1713093568</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2405,7 +2463,7 @@
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
+          <t>Bathroom.WaterHeater001.state: on</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2413,6 +2471,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2431,7 +2490,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1710300669</v>
+        <v>1713102018</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2441,7 +2500,7 @@
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: on</t>
+          <t>Bathroom.WaterHeater001.state: off</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -2449,6 +2508,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2467,7 +2527,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1710301633</v>
+        <v>1713108541</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2485,6 +2545,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2503,7 +2564,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1710307251</v>
+        <v>1713139645</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2521,6 +2582,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2539,7 +2601,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1710318466</v>
+        <v>1713226109</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2557,6 +2619,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2575,7 +2638,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1710319918</v>
+        <v>1713264406</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2590,9 +2653,10 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2611,7 +2675,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1710322100</v>
+        <v>1713276211</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2629,6 +2693,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2647,7 +2712,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1710330052</v>
+        <v>1713277067</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2665,6 +2730,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2683,7 +2749,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1710373133</v>
+        <v>1713279031</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2701,6 +2767,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2719,7 +2786,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1710374656</v>
+        <v>1713310473</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2737,6 +2804,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2755,7 +2823,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1710387019</v>
+        <v>1713348446</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2773,6 +2841,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2791,7 +2860,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1710392103</v>
+        <v>1713349045</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2801,7 +2870,7 @@
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
+          <t>Bathroom.WaterHeater001.state: on</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2809,6 +2878,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2827,7 +2897,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1710400554</v>
+        <v>1713350809</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2837,7 +2907,7 @@
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: on</t>
+          <t>Bathroom.WaterHeater001.state: off</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -2845,6 +2915,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2863,7 +2934,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1710401843</v>
+        <v>1713355704</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2873,7 +2944,7 @@
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
+          <t>Bathroom.WaterHeater001.state: on</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -2881,6 +2952,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2899,7 +2971,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1710409412</v>
+        <v>1713575371</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2917,6 +2989,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2935,7 +3008,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1710485994</v>
+        <v>1713591688</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2950,9 +3023,10 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2971,7 +3045,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1710488265</v>
+        <v>1713593449</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2989,6 +3063,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3007,7 +3082,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1710488999</v>
+        <v>1713604627</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3022,9 +3097,10 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3043,7 +3119,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1710494896</v>
+        <v>1713609219</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3061,6 +3137,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3079,7 +3156,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1710562188</v>
+        <v>1713612170</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -3094,9 +3171,10 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3115,7 +3193,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1710569277</v>
+        <v>1713614030</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3133,6 +3211,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3151,7 +3230,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1710569515</v>
+        <v>1713624173</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3161,14 +3240,15 @@
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: on</t>
+          <t>Bathroom.WaterHeater001.state: off</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3187,7 +3267,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1710572071</v>
+        <v>1713626146</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3197,7 +3277,7 @@
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
+          <t>Bathroom.WaterHeater001.state: on</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3205,6 +3285,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3223,7 +3304,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1710572090</v>
+        <v>1713659532</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3241,6 +3322,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3259,7 +3341,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1710576795</v>
+        <v>1713660897</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -3269,14 +3351,15 @@
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
+          <t>Bathroom.WaterHeater001.state: on</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3295,7 +3378,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1710651915</v>
+        <v>1713663719</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3305,14 +3388,15 @@
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: on</t>
+          <t>Bathroom.WaterHeater001.state: off</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3331,7 +3415,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1710749780</v>
+        <v>1713665748</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3341,7 +3425,7 @@
       <c r="F81" t="inlineStr"/>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
+          <t>Bathroom.WaterHeater001.state: on</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -3349,6 +3433,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3367,7 +3452,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1710800789</v>
+        <v>1713667256</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3385,6 +3470,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3403,7 +3489,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1710829781</v>
+        <v>1713675606</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3418,9 +3504,10 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3439,7 +3526,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1710830863</v>
+        <v>1713677534</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3457,6 +3544,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3475,7 +3563,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1710833925</v>
+        <v>1713682565</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3490,9 +3578,10 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3511,7 +3600,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1710835655</v>
+        <v>1713688362</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3529,6 +3618,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3547,7 +3637,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1710837987</v>
+        <v>1713690186</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3562,9 +3652,10 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3583,7 +3674,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1710890030</v>
+        <v>1713692350</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3601,6 +3692,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3619,7 +3711,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1710890843</v>
+        <v>1713700901</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3629,7 +3721,7 @@
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
+          <t>Bathroom.WaterHeater001.state: on</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -3637,6 +3729,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3655,7 +3748,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1710900076</v>
+        <v>1713702344</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3665,7 +3758,7 @@
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: on</t>
+          <t>Bathroom.WaterHeater001.state: off</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -3673,6 +3766,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3691,7 +3785,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1710901847</v>
+        <v>1713707081</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3709,6 +3803,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3727,7 +3822,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1710912788</v>
+        <v>1713771860</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3737,14 +3832,15 @@
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
+          <t>Bathroom.WaterHeater001.state: on</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3763,7 +3859,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1710916773</v>
+        <v>1713779435</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3773,7 +3869,7 @@
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: on</t>
+          <t>Bathroom.WaterHeater001.state: off</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -3781,6 +3877,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3799,7 +3896,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1710917698</v>
+        <v>1713864451</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3809,14 +3906,15 @@
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
+          <t>Bathroom.WaterHeater001.state: on</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3835,7 +3933,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1710919375</v>
+        <v>1713866854</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3845,7 +3943,7 @@
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: on</t>
+          <t>Bathroom.WaterHeater001.state: off</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -3853,6 +3951,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3871,7 +3970,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1710920453</v>
+        <v>1713875456</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3881,7 +3980,7 @@
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
+          <t>Bathroom.WaterHeater001.state: on</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -3889,6 +3988,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3907,7 +4007,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1710924826</v>
+        <v>1713952920</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3917,7 +4017,7 @@
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: on</t>
+          <t>Bathroom.WaterHeater001.state: off</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -3925,6 +4025,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3943,7 +4044,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1710977152</v>
+        <v>1714001310</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3953,7 +4054,7 @@
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
+          <t>Bathroom.WaterHeater001.state: on</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -3961,6 +4062,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3979,7 +4081,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1710977355</v>
+        <v>1714038750</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3989,14 +4091,15 @@
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: on</t>
+          <t>Bathroom.WaterHeater001.state: off</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4015,7 +4118,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1710980050</v>
+        <v>1714043038</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -4025,7 +4128,7 @@
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
+          <t>Bathroom.WaterHeater001.state: on</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4033,6 +4136,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4051,7 +4155,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1710988384</v>
+        <v>1714179171</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -4061,7 +4165,7 @@
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: on</t>
+          <t>Bathroom.WaterHeater001.state: off</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4069,6 +4173,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4087,7 +4192,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1710989672</v>
+        <v>1714181969</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -4105,6 +4210,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4123,7 +4229,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1710992419</v>
+        <v>1714181979</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -4133,7 +4239,7 @@
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
+          <t>Bathroom.WaterHeater001.state: on</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4141,6 +4247,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4159,7 +4266,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1711000541</v>
+        <v>1714183477</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -4169,7 +4276,7 @@
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: on</t>
+          <t>Bathroom.WaterHeater001.state: off</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4177,6 +4284,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4195,7 +4303,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1711008989</v>
+        <v>1714211311</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4205,14 +4313,15 @@
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
+          <t>Bathroom.WaterHeater001.state: on</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4231,7 +4340,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1711011409</v>
+        <v>1714214754</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -4249,6 +4358,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4267,7 +4377,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1711014305</v>
+        <v>1714222715</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -4277,14 +4387,15 @@
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
+          <t>Bathroom.WaterHeater001.state: on</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>physical</t>
-        </is>
-      </c>
+          <t>cyber</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4303,7 +4414,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1711058891</v>
+        <v>1714225458</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -4321,6 +4432,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4339,7 +4451,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1711061031</v>
+        <v>1714231662</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -4357,6 +4469,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4375,7 +4488,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1711085132</v>
+        <v>1714266543</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -4393,6 +4506,7 @@
           <t>cyber</t>
         </is>
       </c>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4411,7 +4525,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1711087088</v>
+        <v>1714271049</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -4429,6 +4543,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4447,7 +4562,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1711098736</v>
+        <v>1714271868</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4465,6 +4580,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4483,7 +4599,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1711175703</v>
+        <v>1714273724</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4501,6 +4617,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4519,7 +4636,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1711176742</v>
+        <v>1714297120</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4534,9 +4651,10 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>cyber</t>
-        </is>
-      </c>
+          <t>physical</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4555,7 +4673,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1711184021</v>
+        <v>1714298464</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4573,6 +4691,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4591,7 +4710,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1711236361</v>
+        <v>1714302984</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4601,7 +4720,7 @@
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: on</t>
+          <t>Bathroom.WaterHeater001.state: off</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -4609,6 +4728,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4627,7 +4747,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1711275193</v>
+        <v>1714306541</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4637,7 +4757,7 @@
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
+          <t>Bathroom.WaterHeater001.state: on</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -4645,6 +4765,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4663,7 +4784,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1711319418</v>
+        <v>1714307748</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4681,6 +4802,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4699,7 +4821,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1711350511</v>
+        <v>1714313051</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4717,798 +4839,7 @@
           <t>physical</t>
         </is>
       </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>WaterHeater_Operation</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Bathroom</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>1711355180</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr"/>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
-        </is>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>WaterHeater_Operation</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Bathroom</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>1711355343</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr"/>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>Bathroom.WaterHeater001.state: on</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>cyber</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>WaterHeater_Operation</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Bathroom</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>1711358124</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr"/>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>WaterHeater_Operation</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Bathroom</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>1711360094</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr"/>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>WaterHeater_Operation</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Bathroom</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>1711360508</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr"/>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>Bathroom.WaterHeater001.state: on</t>
-        </is>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>WaterHeater_Operation</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Bathroom</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>1711452395</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr"/>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
-        </is>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>WaterHeater_Operation</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Bathroom</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>1711501878</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr"/>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>Bathroom.WaterHeater001.state: on</t>
-        </is>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>cyber</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>WaterHeater_Operation</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Bathroom</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>1711504723</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr"/>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>WaterHeater_Operation</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Bathroom</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>1711518526</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr"/>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>Bathroom.WaterHeater001.state: on</t>
-        </is>
-      </c>
-      <c r="H128" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>WaterHeater_Operation</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Bathroom</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>1711520644</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr"/>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>WaterHeater_Operation</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Bathroom</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>1711542027</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr"/>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>Bathroom.WaterHeater001.state: on</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>WaterHeater_Operation</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Bathroom</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>1711544276</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr"/>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>WaterHeater_Operation</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Bathroom</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>1711546143</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr"/>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>WaterHeater_Operation</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Bathroom</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>1711548792</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr"/>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>WaterHeater_Operation</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Bathroom</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>1711556069</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr"/>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>Bathroom.WaterHeater001.state: on</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>WaterHeater_Operation</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Bathroom</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>1711591141</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
-        </is>
-      </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>WaterHeater_Operation</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Bathroom</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>1711605919</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>Bathroom.WaterHeater001.state: on</t>
-        </is>
-      </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>WaterHeater_Operation</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Bathroom</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>1711607871</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr"/>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>WaterHeater_Operation</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Bathroom</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>1711620418</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr"/>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>Bathroom.WaterHeater001.state: on</t>
-        </is>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>cyber</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>WaterHeater_Operation</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Bathroom</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>1711621464</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>WaterHeater_Operation</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Bathroom</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>1711623565</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr"/>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>Bathroom.WaterHeater001.state: off</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>WaterHeater_Operation</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Bathroom</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>1711625478</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr"/>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>Bathroom.WaterHeater001.state: on</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
+      <c r="I119" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
